--- a/Main/AUT_EEC_results/AUT_EEC_SIDIS_a0.01_b0.01_x0.30_Q100_LO.xlsx
+++ b/Main/AUT_EEC_results/AUT_EEC_SIDIS_a0.01_b0.01_x0.30_Q100_LO.xlsx
@@ -455,10 +455,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02768353931638681</v>
+        <v>0.01365054996452216</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02768353931638681</v>
+        <v>0.01365054996452216</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -469,10 +469,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.07505380710733438</v>
+        <v>0.03797918645931136</v>
       </c>
       <c r="C3" t="n">
-        <v>0.07505380710733438</v>
+        <v>0.03797918645931136</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -483,10 +483,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.1567537163598545</v>
+        <v>0.07903519858329003</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1567537163598545</v>
+        <v>0.07903519858329003</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -497,10 +497,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.2134613293958428</v>
+        <v>0.1077949590573593</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2134613293958428</v>
+        <v>0.1077949590573593</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -511,10 +511,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.2065822789854307</v>
+        <v>0.104117924799867</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2065822789854307</v>
+        <v>0.104117924799867</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -525,10 +525,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.1861466286161687</v>
+        <v>0.09393625605415444</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1861466286161687</v>
+        <v>0.09393625605415444</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -539,10 +539,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.1686278423183173</v>
+        <v>0.08527180409673281</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1686278423183173</v>
+        <v>0.08527180409673281</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -553,10 +553,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.1581056230621427</v>
+        <v>0.07999193357034765</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1581056230621427</v>
+        <v>0.07999193357034765</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
